--- a/SensitivityAnalysis/LeaveOneOut/Gwas/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/Gwas/loo.xlsx
@@ -157,10 +157,10 @@
         <v>0.8150727019066166</v>
       </c>
       <c r="D2" t="n">
+        <v>0.9886906830220008</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.6414547207912324</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.9886906830220008</v>
       </c>
       <c r="F2" t="n">
         <v>0.08858060260988987</v>
@@ -180,10 +180,10 @@
         <v>0.958957982139458</v>
       </c>
       <c r="D3" t="n">
+        <v>1.0521498211441167</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.8657661431347994</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.0521498211441167</v>
       </c>
       <c r="F3" t="n">
         <v>0.04754685663502996</v>
@@ -203,10 +203,10 @@
         <v>0.929164421241809</v>
       </c>
       <c r="D4" t="n">
+        <v>1.1941244101019575</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.6642044323816605</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.1941244101019575</v>
       </c>
       <c r="F4" t="n">
         <v>0.13518366778579002</v>
@@ -226,10 +226,10 @@
         <v>0.68366007454613</v>
       </c>
       <c r="D5" t="n">
+        <v>0.8452354080097176</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.5220847410825423</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.8452354080097176</v>
       </c>
       <c r="F5" t="n">
         <v>0.08243639462427942</v>
@@ -249,10 +249,10 @@
         <v>0.8145622561240954</v>
       </c>
       <c r="D6" t="n">
+        <v>1.0089283865600644</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.6201961256881263</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.0089283865600644</v>
       </c>
       <c r="F6" t="n">
         <v>0.09916639307957603</v>
@@ -272,10 +272,10 @@
         <v>0.7436877270443805</v>
       </c>
       <c r="D7" t="n">
+        <v>0.9066110072031471</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.5807644468856138</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9066110072031471</v>
       </c>
       <c r="F7" t="n">
         <v>0.08312412252998298</v>
@@ -295,10 +295,10 @@
         <v>0.8120053180837921</v>
       </c>
       <c r="D8" t="n">
+        <v>1.000833777132605</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.623176859034979</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.000833777132605</v>
       </c>
       <c r="F8" t="n">
         <v>0.0963410505351087</v>
@@ -349,10 +349,10 @@
         <v>-1.4015776287277675</v>
       </c>
       <c r="D2" t="n">
+        <v>-1.053031397760546</v>
+      </c>
+      <c r="E2" t="n">
         <v>-1.7501238596949888</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1.053031397760546</v>
       </c>
       <c r="F2" t="n">
         <v>0.17782970967715372</v>
@@ -372,10 +372,10 @@
         <v>-1.6807401761764733</v>
       </c>
       <c r="D3" t="n">
+        <v>-1.4753152728738055</v>
+      </c>
+      <c r="E3" t="n">
         <v>-1.8861650794791411</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.4753152728738055</v>
       </c>
       <c r="F3" t="n">
         <v>0.10480862413401414</v>
@@ -395,10 +395,10 @@
         <v>-1.6583639765829643</v>
       </c>
       <c r="D4" t="n">
+        <v>-1.1496120126156586</v>
+      </c>
+      <c r="E4" t="n">
         <v>-2.16711594055027</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1.1496120126156586</v>
       </c>
       <c r="F4" t="n">
         <v>0.25956732855474784</v>
@@ -418,10 +418,10 @@
         <v>-1.1362689954192724</v>
       </c>
       <c r="D5" t="n">
+        <v>-0.8042536136278073</v>
+      </c>
+      <c r="E5" t="n">
         <v>-1.4682843772107375</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.8042536136278073</v>
       </c>
       <c r="F5" t="n">
         <v>0.1693956029548291</v>
@@ -441,10 +441,10 @@
         <v>-1.4001473703893499</v>
       </c>
       <c r="D6" t="n">
+        <v>-1.0127425945539748</v>
+      </c>
+      <c r="E6" t="n">
         <v>-1.787552146224725</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1.0127425945539748</v>
       </c>
       <c r="F6" t="n">
         <v>0.19765549787519135</v>
@@ -464,10 +464,10 @@
         <v>-1.254056622147238</v>
       </c>
       <c r="D7" t="n">
+        <v>-0.9272057066225883</v>
+      </c>
+      <c r="E7" t="n">
         <v>-1.5809075376718877</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.9272057066225883</v>
       </c>
       <c r="F7" t="n">
         <v>0.16676067118604576</v>
@@ -487,10 +487,10 @@
         <v>-1.3946168092302955</v>
       </c>
       <c r="D8" t="n">
+        <v>-1.0107499072493833</v>
+      </c>
+      <c r="E8" t="n">
         <v>-1.7784837112112077</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-1.0107499072493833</v>
       </c>
       <c r="F8" t="n">
         <v>0.19585046019434302</v>
@@ -541,10 +541,10 @@
         <v>0.2214099332546395</v>
       </c>
       <c r="D2" t="n">
+        <v>0.29970864784150014</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.14311121866777887</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.29970864784150014</v>
       </c>
       <c r="F2" t="n">
         <v>0.03994832376880646</v>
@@ -564,10 +564,10 @@
         <v>0.2822261088617243</v>
       </c>
       <c r="D3" t="n">
+        <v>0.35629621092055136</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.2081560068028972</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.35629621092055136</v>
       </c>
       <c r="F3" t="n">
         <v>0.03779086839736076</v>
@@ -587,10 +587,10 @@
         <v>0.2749365150111475</v>
       </c>
       <c r="D4" t="n">
+        <v>0.39385236502688503</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.15602066499540998</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.39385236502688503</v>
       </c>
       <c r="F4" t="n">
         <v>0.06067135204884568</v>
@@ -610,10 +610,10 @@
         <v>0.15467793989100037</v>
       </c>
       <c r="D5" t="n">
+        <v>0.23242527637208388</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.07693060340991685</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.23242527637208388</v>
       </c>
       <c r="F5" t="n">
         <v>0.039667008408716085</v>
@@ -633,10 +633,10 @@
         <v>0.2218264079630959</v>
       </c>
       <c r="D6" t="n">
+        <v>0.3092949595835319</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.13435785634265993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.3092949595835319</v>
       </c>
       <c r="F6" t="n">
         <v>0.04462681205124285</v>
@@ -656,10 +656,10 @@
         <v>0.1801278962306344</v>
       </c>
       <c r="D7" t="n">
+        <v>0.24672147493106045</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.11353431753020837</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.24672147493106045</v>
       </c>
       <c r="F7" t="n">
         <v>0.03397631566348267</v>
@@ -679,10 +679,10 @@
         <v>0.22164496416222204</v>
       </c>
       <c r="D8" t="n">
+        <v>0.30922349534375254</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.13406643298069154</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.30922349534375254</v>
       </c>
       <c r="F8" t="n">
         <v>0.04468292407220943</v>
@@ -733,10 +733,10 @@
         <v>0.24660765941256563</v>
       </c>
       <c r="D2" t="n">
+        <v>0.32400141661333626</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.16921390221179503</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.32400141661333626</v>
       </c>
       <c r="F2" t="n">
         <v>0.0394866108167197</v>
@@ -756,10 +756,10 @@
         <v>0.2766374904761365</v>
       </c>
       <c r="D3" t="n">
+        <v>0.37446213771096715</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.17881284324130586</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.37446213771096715</v>
       </c>
       <c r="F3" t="n">
         <v>0.04991053430348503</v>
@@ -779,10 +779,10 @@
         <v>0.28283726897943673</v>
       </c>
       <c r="D4" t="n">
+        <v>0.4044935394381231</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.16118099852075035</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.4044935394381231</v>
       </c>
       <c r="F4" t="n">
         <v>0.062069525744227735</v>
@@ -802,10 +802,10 @@
         <v>0.22431520803782024</v>
       </c>
       <c r="D5" t="n">
+        <v>0.3272216781266889</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.12140873794895159</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.3272216781266889</v>
       </c>
       <c r="F5" t="n">
         <v>0.05250330106574931</v>
@@ -825,10 +825,10 @@
         <v>0.24633914912842206</v>
       </c>
       <c r="D6" t="n">
+        <v>0.32386716445467256</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.16881113380217153</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.32386716445467256</v>
       </c>
       <c r="F6" t="n">
         <v>0.03955510986033191</v>
@@ -848,10 +848,10 @@
         <v>0.23178300664381848</v>
       </c>
       <c r="D7" t="n">
+        <v>0.31973424322697425</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.14383177006066272</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.31973424322697425</v>
       </c>
       <c r="F7" t="n">
         <v>0.044873079889365196</v>
@@ -871,10 +871,10 @@
         <v>0.24491022426710443</v>
       </c>
       <c r="D8" t="n">
+        <v>0.3224213303432177</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.16739911819099118</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3224213303432177</v>
       </c>
       <c r="F8" t="n">
         <v>0.039546482691894515</v>
@@ -925,10 +925,10 @@
         <v>0.15314889286551586</v>
       </c>
       <c r="D2" t="n">
+        <v>0.22608216244919438</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.08021562328183733</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.22608216244919438</v>
       </c>
       <c r="F2" t="n">
         <v>0.037210851828407415</v>
@@ -948,10 +948,10 @@
         <v>0.13787416178828812</v>
       </c>
       <c r="D3" t="n">
+        <v>0.2287090740502245</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.047039249526351745</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.2287090740502245</v>
       </c>
       <c r="F3" t="n">
         <v>0.04634434299078387</v>
@@ -971,10 +971,10 @@
         <v>0.09940528747806154</v>
       </c>
       <c r="D4" t="n">
+        <v>0.21140875429009073</v>
+      </c>
+      <c r="E4" t="n">
         <v>-0.012598179333967646</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.21140875429009073</v>
       </c>
       <c r="F4" t="n">
         <v>0.05714462592450469</v>
@@ -994,10 +994,10 @@
         <v>0.1515433028216228</v>
       </c>
       <c r="D5" t="n">
+        <v>0.24988718118955577</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.05319942445368979</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.24988718118955577</v>
       </c>
       <c r="F5" t="n">
         <v>0.05017544814690459</v>
@@ -1017,10 +1017,10 @@
         <v>0.15353609266003612</v>
       </c>
       <c r="D6" t="n">
+        <v>0.2265292248753773</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.08054296044469496</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.2265292248753773</v>
       </c>
       <c r="F6" t="n">
         <v>0.037241393987418964</v>
@@ -1040,10 +1040,10 @@
         <v>0.17711870535326196</v>
       </c>
       <c r="D7" t="n">
+        <v>0.2609891324822588</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.09324827822426512</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.2609891324822588</v>
       </c>
       <c r="F7" t="n">
         <v>0.042791034249488186</v>
@@ -1063,10 +1063,10 @@
         <v>0.15540268423600592</v>
       </c>
       <c r="D8" t="n">
+        <v>0.2285806264167417</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.08222474205527015</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.2285806264167417</v>
       </c>
       <c r="F8" t="n">
         <v>0.03733568478608968</v>
@@ -1117,10 +1117,10 @@
         <v>0.0145034658338371</v>
       </c>
       <c r="D2" t="n">
+        <v>0.023794077247097173</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.005212854420577029</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.023794077247097173</v>
       </c>
       <c r="F2" t="n">
         <v>0.0047401078639082</v>
@@ -1140,10 +1140,10 @@
         <v>0.019360019488255727</v>
       </c>
       <c r="D3" t="n">
+        <v>0.031124405274854605</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.007595633701656848</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.031124405274854605</v>
       </c>
       <c r="F3" t="n">
         <v>0.006002237646223918</v>
@@ -1163,10 +1163,10 @@
         <v>0.021051036687392576</v>
       </c>
       <c r="D4" t="n">
+        <v>0.035517066336144695</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.006585007038640459</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.035517066336144695</v>
       </c>
       <c r="F4" t="n">
         <v>0.007380627371812305</v>
@@ -1186,10 +1186,10 @@
         <v>0.010632309428418755</v>
       </c>
       <c r="D5" t="n">
+        <v>0.022912937695795367</v>
+      </c>
+      <c r="E5" t="n">
         <v>-0.0016483188389578574</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.022912937695795367</v>
       </c>
       <c r="F5" t="n">
         <v>0.006265626667028884</v>
@@ -1209,10 +1209,10 @@
         <v>0.014165643121438486</v>
       </c>
       <c r="D6" t="n">
+        <v>0.023475622237700958</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.004855664005176017</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.023475622237700958</v>
       </c>
       <c r="F6" t="n">
         <v>0.0047499893450318725</v>
@@ -1232,10 +1232,10 @@
         <v>0.011423134114756543</v>
       </c>
       <c r="D7" t="n">
+        <v>0.021978984252173307</v>
+      </c>
+      <c r="E7" t="n">
         <v>8.672839773397785E-4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.021978984252173307</v>
       </c>
       <c r="F7" t="n">
         <v>0.005385637825212635</v>
@@ -1255,10 +1255,10 @@
         <v>0.014610727283375412</v>
       </c>
       <c r="D8" t="n">
+        <v>0.023920381806876917</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.005301072759873909</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.023920381806876917</v>
       </c>
       <c r="F8" t="n">
         <v>0.004749823736480359</v>
@@ -1306,19 +1306,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.23011913258685218</v>
+        <v>0.23236872185860305</v>
       </c>
       <c r="D2" t="n">
-        <v>0.14925497334793525</v>
+        <v>0.3126228873439243</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3109832918257691</v>
+        <v>0.15211455637328183</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04125722410148824</v>
+        <v>0.04094600279863327</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4376317070633728E-8</v>
+        <v>1.3868556953420557E-8</v>
       </c>
     </row>
     <row r="3">
@@ -1332,10 +1332,10 @@
         <v>0.2704071762944307</v>
       </c>
       <c r="D3" t="n">
+        <v>0.37273502795706925</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.1680793246317921</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.37273502795706925</v>
       </c>
       <c r="F3" t="n">
         <v>0.05220808758297887</v>
@@ -1352,19 +1352,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.25061593595347764</v>
+        <v>0.2513627110257794</v>
       </c>
       <c r="D4" t="n">
-        <v>0.12174242986144707</v>
+        <v>0.3776934934157469</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3794894420455082</v>
+        <v>0.1250319286358119</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06575178882246459</v>
+        <v>0.06445448081120791</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3810061859872023E-4</v>
+        <v>9.625289401307472E-5</v>
       </c>
     </row>
     <row r="5">
@@ -1375,19 +1375,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.17922574152039694</v>
+        <v>0.1854429807896794</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07163962854112237</v>
+        <v>0.29141199045302524</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2868118544996715</v>
+        <v>0.07947397112633359</v>
       </c>
       <c r="F5" t="n">
-        <v>0.054890873969017644</v>
+        <v>0.054065821256809095</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0010941453602373464</v>
+        <v>6.036958902436025E-4</v>
       </c>
     </row>
     <row r="6">
@@ -1398,19 +1398,19 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>0.199746242275233</v>
+        <v>0.2035612307075541</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1073265999775972</v>
+        <v>0.2950206438251673</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2921658845728688</v>
+        <v>0.11210181758994091</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04715287872328357</v>
+        <v>0.046662965876333264</v>
       </c>
       <c r="G6" t="n">
-        <v>2.273940281587897E-5</v>
+        <v>1.286596734507788E-5</v>
       </c>
     </row>
     <row r="7">
@@ -1421,19 +1421,19 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>0.23544755268366943</v>
+        <v>0.2376478397950334</v>
       </c>
       <c r="D7" t="n">
-        <v>0.15400467660878223</v>
+        <v>0.3184679548594908</v>
       </c>
       <c r="E7" t="n">
-        <v>0.31689042875855666</v>
+        <v>0.156827724730576</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0415524877933098</v>
+        <v>0.04123475258390683</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4594077711538749E-8</v>
+        <v>8.248984450105824E-9</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/LeaveOneOut/Gwas/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/Gwas/loo.xlsx
@@ -154,19 +154,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8150727019066166</v>
+        <v>0.8169972721519051</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9886906830220008</v>
+        <v>0.6449674875535427</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6414547207912324</v>
+        <v>0.9890270567502675</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08858060260988987</v>
+        <v>0.08777029826447058</v>
       </c>
       <c r="G2" t="n">
-        <v>3.530508621360337E-20</v>
+        <v>1.2982495603869879E-20</v>
       </c>
     </row>
     <row r="3">
@@ -180,10 +180,10 @@
         <v>0.958957982139458</v>
       </c>
       <c r="D3" t="n">
+        <v>0.8657661431347994</v>
+      </c>
+      <c r="E3" t="n">
         <v>1.0521498211441167</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.8657661431347994</v>
       </c>
       <c r="F3" t="n">
         <v>0.04754685663502996</v>
@@ -200,19 +200,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.929164421241809</v>
+        <v>0.9309753625554879</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1941244101019575</v>
+        <v>0.6692038190732308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6642044323816605</v>
+        <v>1.192746906037745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.13518366778579002</v>
+        <v>0.13355690993992705</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2712233566670805E-12</v>
+        <v>3.1553220295590462E-12</v>
       </c>
     </row>
     <row r="5">
@@ -223,19 +223,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.68366007454613</v>
+        <v>0.6868592584970361</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8452354080097176</v>
+        <v>0.5259396154909102</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5220847410825423</v>
+        <v>0.847778901503162</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08243639462427942</v>
+        <v>0.08210185867659489</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1025787183979442E-16</v>
+        <v>5.963732581346879E-17</v>
       </c>
     </row>
     <row r="6">
@@ -246,19 +246,19 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8145622561240954</v>
+        <v>0.8164925909255152</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0089283865600644</v>
+        <v>0.6239029298709453</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6201961256881263</v>
+        <v>1.009082251980085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09916639307957603</v>
+        <v>0.09826003115029072</v>
       </c>
       <c r="G6" t="n">
-        <v>2.137688156122437E-16</v>
+        <v>9.609905150903697E-17</v>
       </c>
     </row>
     <row r="7">
@@ -269,19 +269,19 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7436877270443805</v>
+        <v>0.7460854043396331</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9066110072031471</v>
+        <v>0.5847234021361076</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5807644468856138</v>
+        <v>0.9074474065431586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08312412252998298</v>
+        <v>0.08232755214465584</v>
       </c>
       <c r="G7" t="n">
-        <v>3.662225017387154E-19</v>
+        <v>1.2760847818374233E-19</v>
       </c>
     </row>
     <row r="8">
@@ -292,19 +292,19 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8120053180837921</v>
+        <v>0.8139321469487153</v>
       </c>
       <c r="D8" t="n">
-        <v>1.000833777132605</v>
+        <v>0.6269156719775002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.623176859034979</v>
+        <v>1.0009486219199304</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0963410505351087</v>
+        <v>0.09541656886286487</v>
       </c>
       <c r="G8" t="n">
-        <v>3.502864916005451E-17</v>
+        <v>1.459661765085205E-17</v>
       </c>
     </row>
   </sheetData>
@@ -349,10 +349,10 @@
         <v>-1.4015776287277675</v>
       </c>
       <c r="D2" t="n">
+        <v>-1.7501238596949888</v>
+      </c>
+      <c r="E2" t="n">
         <v>-1.053031397760546</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1.7501238596949888</v>
       </c>
       <c r="F2" t="n">
         <v>0.17782970967715372</v>
@@ -372,10 +372,10 @@
         <v>-1.6807401761764733</v>
       </c>
       <c r="D3" t="n">
+        <v>-1.8861650794791411</v>
+      </c>
+      <c r="E3" t="n">
         <v>-1.4753152728738055</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.8861650794791411</v>
       </c>
       <c r="F3" t="n">
         <v>0.10480862413401414</v>
@@ -395,10 +395,10 @@
         <v>-1.6583639765829643</v>
       </c>
       <c r="D4" t="n">
+        <v>-2.16711594055027</v>
+      </c>
+      <c r="E4" t="n">
         <v>-1.1496120126156586</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-2.16711594055027</v>
       </c>
       <c r="F4" t="n">
         <v>0.25956732855474784</v>
@@ -418,10 +418,10 @@
         <v>-1.1362689954192724</v>
       </c>
       <c r="D5" t="n">
+        <v>-1.4682843772107375</v>
+      </c>
+      <c r="E5" t="n">
         <v>-0.8042536136278073</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.4682843772107375</v>
       </c>
       <c r="F5" t="n">
         <v>0.1693956029548291</v>
@@ -441,10 +441,10 @@
         <v>-1.4001473703893499</v>
       </c>
       <c r="D6" t="n">
+        <v>-1.787552146224725</v>
+      </c>
+      <c r="E6" t="n">
         <v>-1.0127425945539748</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1.787552146224725</v>
       </c>
       <c r="F6" t="n">
         <v>0.19765549787519135</v>
@@ -464,10 +464,10 @@
         <v>-1.254056622147238</v>
       </c>
       <c r="D7" t="n">
+        <v>-1.5809075376718877</v>
+      </c>
+      <c r="E7" t="n">
         <v>-0.9272057066225883</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.5809075376718877</v>
       </c>
       <c r="F7" t="n">
         <v>0.16676067118604576</v>
@@ -487,10 +487,10 @@
         <v>-1.3946168092302955</v>
       </c>
       <c r="D8" t="n">
+        <v>-1.7784837112112077</v>
+      </c>
+      <c r="E8" t="n">
         <v>-1.0107499072493833</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-1.7784837112112077</v>
       </c>
       <c r="F8" t="n">
         <v>0.19585046019434302</v>
@@ -541,10 +541,10 @@
         <v>0.2214099332546395</v>
       </c>
       <c r="D2" t="n">
+        <v>0.14311121866777887</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.29970864784150014</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.14311121866777887</v>
       </c>
       <c r="F2" t="n">
         <v>0.03994832376880646</v>
@@ -564,10 +564,10 @@
         <v>0.2822261088617243</v>
       </c>
       <c r="D3" t="n">
+        <v>0.2081560068028972</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.35629621092055136</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.2081560068028972</v>
       </c>
       <c r="F3" t="n">
         <v>0.03779086839736076</v>
@@ -587,10 +587,10 @@
         <v>0.2749365150111475</v>
       </c>
       <c r="D4" t="n">
+        <v>0.15602066499540998</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.39385236502688503</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.15602066499540998</v>
       </c>
       <c r="F4" t="n">
         <v>0.06067135204884568</v>
@@ -610,10 +610,10 @@
         <v>0.15467793989100037</v>
       </c>
       <c r="D5" t="n">
+        <v>0.07693060340991685</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.23242527637208388</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.07693060340991685</v>
       </c>
       <c r="F5" t="n">
         <v>0.039667008408716085</v>
@@ -633,10 +633,10 @@
         <v>0.2218264079630959</v>
       </c>
       <c r="D6" t="n">
+        <v>0.13435785634265993</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.3092949595835319</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.13435785634265993</v>
       </c>
       <c r="F6" t="n">
         <v>0.04462681205124285</v>
@@ -656,10 +656,10 @@
         <v>0.1801278962306344</v>
       </c>
       <c r="D7" t="n">
+        <v>0.11353431753020837</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.24672147493106045</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.11353431753020837</v>
       </c>
       <c r="F7" t="n">
         <v>0.03397631566348267</v>
@@ -679,10 +679,10 @@
         <v>0.22164496416222204</v>
       </c>
       <c r="D8" t="n">
+        <v>0.13406643298069154</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.30922349534375254</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.13406643298069154</v>
       </c>
       <c r="F8" t="n">
         <v>0.04468292407220943</v>
@@ -733,10 +733,10 @@
         <v>0.24660765941256563</v>
       </c>
       <c r="D2" t="n">
+        <v>0.16921390221179503</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.32400141661333626</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.16921390221179503</v>
       </c>
       <c r="F2" t="n">
         <v>0.0394866108167197</v>
@@ -756,10 +756,10 @@
         <v>0.2766374904761365</v>
       </c>
       <c r="D3" t="n">
+        <v>0.17881284324130586</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.37446213771096715</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.17881284324130586</v>
       </c>
       <c r="F3" t="n">
         <v>0.04991053430348503</v>
@@ -779,10 +779,10 @@
         <v>0.28283726897943673</v>
       </c>
       <c r="D4" t="n">
+        <v>0.16118099852075035</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.4044935394381231</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.16118099852075035</v>
       </c>
       <c r="F4" t="n">
         <v>0.062069525744227735</v>
@@ -802,10 +802,10 @@
         <v>0.22431520803782024</v>
       </c>
       <c r="D5" t="n">
+        <v>0.12140873794895159</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.3272216781266889</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.12140873794895159</v>
       </c>
       <c r="F5" t="n">
         <v>0.05250330106574931</v>
@@ -825,10 +825,10 @@
         <v>0.24633914912842206</v>
       </c>
       <c r="D6" t="n">
+        <v>0.16881113380217153</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.32386716445467256</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.16881113380217153</v>
       </c>
       <c r="F6" t="n">
         <v>0.03955510986033191</v>
@@ -848,10 +848,10 @@
         <v>0.23178300664381848</v>
       </c>
       <c r="D7" t="n">
+        <v>0.14383177006066272</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.31973424322697425</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.14383177006066272</v>
       </c>
       <c r="F7" t="n">
         <v>0.044873079889365196</v>
@@ -871,10 +871,10 @@
         <v>0.24491022426710443</v>
       </c>
       <c r="D8" t="n">
+        <v>0.16739911819099118</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.3224213303432177</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.16739911819099118</v>
       </c>
       <c r="F8" t="n">
         <v>0.039546482691894515</v>
@@ -925,10 +925,10 @@
         <v>0.15314889286551586</v>
       </c>
       <c r="D2" t="n">
+        <v>0.08021562328183733</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.22608216244919438</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.08021562328183733</v>
       </c>
       <c r="F2" t="n">
         <v>0.037210851828407415</v>
@@ -948,10 +948,10 @@
         <v>0.13787416178828812</v>
       </c>
       <c r="D3" t="n">
+        <v>0.047039249526351745</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.2287090740502245</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.047039249526351745</v>
       </c>
       <c r="F3" t="n">
         <v>0.04634434299078387</v>
@@ -971,10 +971,10 @@
         <v>0.09940528747806154</v>
       </c>
       <c r="D4" t="n">
+        <v>-0.012598179333967646</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.21140875429009073</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.012598179333967646</v>
       </c>
       <c r="F4" t="n">
         <v>0.05714462592450469</v>
@@ -994,10 +994,10 @@
         <v>0.1515433028216228</v>
       </c>
       <c r="D5" t="n">
+        <v>0.05319942445368979</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.24988718118955577</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.05319942445368979</v>
       </c>
       <c r="F5" t="n">
         <v>0.05017544814690459</v>
@@ -1017,10 +1017,10 @@
         <v>0.15353609266003612</v>
       </c>
       <c r="D6" t="n">
+        <v>0.08054296044469496</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.2265292248753773</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.08054296044469496</v>
       </c>
       <c r="F6" t="n">
         <v>0.037241393987418964</v>
@@ -1040,10 +1040,10 @@
         <v>0.17711870535326196</v>
       </c>
       <c r="D7" t="n">
+        <v>0.09324827822426512</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.2609891324822588</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.09324827822426512</v>
       </c>
       <c r="F7" t="n">
         <v>0.042791034249488186</v>
@@ -1063,10 +1063,10 @@
         <v>0.15540268423600592</v>
       </c>
       <c r="D8" t="n">
+        <v>0.08222474205527015</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.2285806264167417</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.08222474205527015</v>
       </c>
       <c r="F8" t="n">
         <v>0.03733568478608968</v>
@@ -1117,10 +1117,10 @@
         <v>0.0145034658338371</v>
       </c>
       <c r="D2" t="n">
+        <v>0.005212854420577029</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.023794077247097173</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.005212854420577029</v>
       </c>
       <c r="F2" t="n">
         <v>0.0047401078639082</v>
@@ -1140,10 +1140,10 @@
         <v>0.019360019488255727</v>
       </c>
       <c r="D3" t="n">
+        <v>0.007595633701656848</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.031124405274854605</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.007595633701656848</v>
       </c>
       <c r="F3" t="n">
         <v>0.006002237646223918</v>
@@ -1163,10 +1163,10 @@
         <v>0.021051036687392576</v>
       </c>
       <c r="D4" t="n">
+        <v>0.006585007038640459</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.035517066336144695</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.006585007038640459</v>
       </c>
       <c r="F4" t="n">
         <v>0.007380627371812305</v>
@@ -1186,10 +1186,10 @@
         <v>0.010632309428418755</v>
       </c>
       <c r="D5" t="n">
+        <v>-0.0016483188389578574</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.022912937695795367</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.0016483188389578574</v>
       </c>
       <c r="F5" t="n">
         <v>0.006265626667028884</v>
@@ -1209,10 +1209,10 @@
         <v>0.014165643121438486</v>
       </c>
       <c r="D6" t="n">
+        <v>0.004855664005176017</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.023475622237700958</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.004855664005176017</v>
       </c>
       <c r="F6" t="n">
         <v>0.0047499893450318725</v>
@@ -1232,10 +1232,10 @@
         <v>0.011423134114756543</v>
       </c>
       <c r="D7" t="n">
+        <v>8.672839773397785E-4</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.021978984252173307</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8.672839773397785E-4</v>
       </c>
       <c r="F7" t="n">
         <v>0.005385637825212635</v>
@@ -1255,10 +1255,10 @@
         <v>0.014610727283375412</v>
       </c>
       <c r="D8" t="n">
+        <v>0.005301072759873909</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.023920381806876917</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.005301072759873909</v>
       </c>
       <c r="F8" t="n">
         <v>0.004749823736480359</v>
@@ -1309,10 +1309,10 @@
         <v>0.23236872185860305</v>
       </c>
       <c r="D2" t="n">
+        <v>0.15211455637328183</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.3126228873439243</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.15211455637328183</v>
       </c>
       <c r="F2" t="n">
         <v>0.04094600279863327</v>
@@ -1332,10 +1332,10 @@
         <v>0.2704071762944307</v>
       </c>
       <c r="D3" t="n">
+        <v>0.1680793246317921</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.37273502795706925</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1680793246317921</v>
       </c>
       <c r="F3" t="n">
         <v>0.05220808758297887</v>
@@ -1355,10 +1355,10 @@
         <v>0.2513627110257794</v>
       </c>
       <c r="D4" t="n">
+        <v>0.1250319286358119</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.3776934934157469</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1250319286358119</v>
       </c>
       <c r="F4" t="n">
         <v>0.06445448081120791</v>
@@ -1378,10 +1378,10 @@
         <v>0.1854429807896794</v>
       </c>
       <c r="D5" t="n">
+        <v>0.07947397112633359</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.29141199045302524</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.07947397112633359</v>
       </c>
       <c r="F5" t="n">
         <v>0.054065821256809095</v>
@@ -1401,10 +1401,10 @@
         <v>0.2035612307075541</v>
       </c>
       <c r="D6" t="n">
+        <v>0.11210181758994091</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.2950206438251673</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.11210181758994091</v>
       </c>
       <c r="F6" t="n">
         <v>0.046662965876333264</v>
@@ -1424,10 +1424,10 @@
         <v>0.2376478397950334</v>
       </c>
       <c r="D7" t="n">
+        <v>0.156827724730576</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.3184679548594908</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.156827724730576</v>
       </c>
       <c r="F7" t="n">
         <v>0.04123475258390683</v>

--- a/SensitivityAnalysis/LeaveOneOut/Gwas/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/Gwas/loo.xlsx
@@ -6,19 +6,19 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Heel bone mineral density" r:id="rId3" sheetId="1"/>
-    <sheet name="Sheet1" r:id="rId4" sheetId="2"/>
-    <sheet name="Coronary artery disease" r:id="rId5" sheetId="3"/>
-    <sheet name="Myocardial infarction" r:id="rId6" sheetId="4"/>
-    <sheet name="Sheet4" r:id="rId7" sheetId="5"/>
-    <sheet name="Non-cancer illness code, self-r" r:id="rId8" sheetId="6"/>
-    <sheet name="Type 2 diabetes" r:id="rId9" sheetId="7"/>
+    <sheet name="eBMD" r:id="rId3" sheetId="1"/>
+    <sheet name="Hip fracture" r:id="rId4" sheetId="2"/>
+    <sheet name="CAD" r:id="rId5" sheetId="3"/>
+    <sheet name="MI" r:id="rId6" sheetId="4"/>
+    <sheet name="IS" r:id="rId7" sheetId="5"/>
+    <sheet name="Hypertension" r:id="rId8" sheetId="6"/>
+    <sheet name="T2DM" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="20">
   <si>
     <t>SNPS</t>
   </si>
@@ -154,19 +154,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8169972721519051</v>
+        <v>0.8150727019066166</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6449674875535427</v>
+        <v>0.6414547207912324</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9890270567502675</v>
+        <v>0.9886906830220008</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08777029826447058</v>
+        <v>0.08858060260988987</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2982495603869879E-20</v>
+        <v>3.530508621360337E-20</v>
       </c>
     </row>
     <row r="3">
@@ -200,19 +200,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9309753625554879</v>
+        <v>0.929164421241809</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6692038190732308</v>
+        <v>0.6642044323816605</v>
       </c>
       <c r="E4" t="n">
-        <v>1.192746906037745</v>
+        <v>1.1941244101019575</v>
       </c>
       <c r="F4" t="n">
-        <v>0.13355690993992705</v>
+        <v>0.13518366778579002</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1553220295590462E-12</v>
+        <v>6.2712233566670805E-12</v>
       </c>
     </row>
     <row r="5">
@@ -223,19 +223,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6868592584970361</v>
+        <v>0.68366007454613</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5259396154909102</v>
+        <v>0.5220847410825423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.847778901503162</v>
+        <v>0.8452354080097176</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08210185867659489</v>
+        <v>0.08243639462427942</v>
       </c>
       <c r="G5" t="n">
-        <v>5.963732581346879E-17</v>
+        <v>1.1025787183979442E-16</v>
       </c>
     </row>
     <row r="6">
@@ -246,19 +246,19 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8164925909255152</v>
+        <v>0.8145622561240954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6239029298709453</v>
+        <v>0.6201961256881263</v>
       </c>
       <c r="E6" t="n">
-        <v>1.009082251980085</v>
+        <v>1.0089283865600644</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09826003115029072</v>
+        <v>0.09916639307957603</v>
       </c>
       <c r="G6" t="n">
-        <v>9.609905150903697E-17</v>
+        <v>2.137688156122437E-16</v>
       </c>
     </row>
     <row r="7">
@@ -269,19 +269,19 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7460854043396331</v>
+        <v>0.7436877270443805</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5847234021361076</v>
+        <v>0.5807644468856138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9074474065431586</v>
+        <v>0.9066110072031471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08232755214465584</v>
+        <v>0.08312412252998298</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2760847818374233E-19</v>
+        <v>3.662225017387154E-19</v>
       </c>
     </row>
     <row r="8">
@@ -292,19 +292,19 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8139321469487153</v>
+        <v>0.8120053180837921</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6269156719775002</v>
+        <v>0.623176859034979</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0009486219199304</v>
+        <v>1.000833777132605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09541656886286487</v>
+        <v>0.0963410505351087</v>
       </c>
       <c r="G8" t="n">
-        <v>1.459661765085205E-17</v>
+        <v>3.502864916005451E-17</v>
       </c>
     </row>
   </sheetData>
@@ -1306,19 +1306,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.23236872185860305</v>
+        <v>0.41316696180467066</v>
       </c>
       <c r="D2" t="n">
-        <v>0.15211455637328183</v>
+        <v>0.3254540976326379</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3126228873439243</v>
+        <v>0.5008798259767034</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04094600279863327</v>
+        <v>0.04475146131226161</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3868556953420557E-8</v>
+        <v>2.6443764249560108E-20</v>
       </c>
     </row>
     <row r="3">
@@ -1329,19 +1329,19 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2704071762944307</v>
+        <v>0.4757526101841174</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1680793246317921</v>
+        <v>0.3922190975470155</v>
       </c>
       <c r="E3" t="n">
-        <v>0.37273502795706925</v>
+        <v>0.5592861228212194</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05220808758297887</v>
+        <v>0.042619139100562205</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2258681765673816E-7</v>
+        <v>6.194704505982911E-29</v>
       </c>
     </row>
     <row r="4">
@@ -1352,19 +1352,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2513627110257794</v>
+        <v>0.4398561459470586</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1250319286358119</v>
+        <v>0.2912878519902936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3776934934157469</v>
+        <v>0.5884244399038235</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06445448081120791</v>
+        <v>0.07580014997794131</v>
       </c>
       <c r="G4" t="n">
-        <v>9.625289401307472E-5</v>
+        <v>6.520098419113803E-9</v>
       </c>
     </row>
     <row r="5">
@@ -1375,19 +1375,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1854429807896794</v>
+        <v>0.34042159073925876</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07947397112633359</v>
+        <v>0.2533406002864186</v>
       </c>
       <c r="E5" t="n">
-        <v>0.29141199045302524</v>
+        <v>0.42750258119209894</v>
       </c>
       <c r="F5" t="n">
-        <v>0.054065821256809095</v>
+        <v>0.04442907676165317</v>
       </c>
       <c r="G5" t="n">
-        <v>6.036958902436025E-4</v>
+        <v>1.82867050575582E-14</v>
       </c>
     </row>
     <row r="6">
@@ -1395,22 +1395,22 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2035612307075541</v>
+        <v>0.41434280201238827</v>
       </c>
       <c r="D6" t="n">
-        <v>0.11210181758994091</v>
+        <v>0.31758817816691953</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2950206438251673</v>
+        <v>0.511097425857857</v>
       </c>
       <c r="F6" t="n">
-        <v>0.046662965876333264</v>
+        <v>0.049364604002790156</v>
       </c>
       <c r="G6" t="n">
-        <v>1.286596734507788E-5</v>
+        <v>4.7179846215941744E-17</v>
       </c>
     </row>
     <row r="7">
@@ -1418,22 +1418,45 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.3715024545649824</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.29658142102791757</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4464234881020472</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.038225017110747356</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.506440996178728E-22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.2376478397950334</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.156827724730576</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.3184679548594908</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.04123475258390683</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8.248984450105824E-9</v>
+      <c r="C8" t="n">
+        <v>0.4146805239667194</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.31920739698151773</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5101536509519211</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04871077907408248</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.6932019693905836E-17</v>
       </c>
     </row>
   </sheetData>
